--- a/Data/Monster.xlsx
+++ b/Data/Monster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5288164-F96C-4D94-9AC8-D46E71EE9183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87C90A29-AA36-47F5-9C63-6E3CE1AB6092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11430" yWindow="9360" windowWidth="25350" windowHeight="10530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Monster" sheetId="1" r:id="rId1"/>
@@ -59,12 +59,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Attack=10;Hp=100;Evasion=10;Accuracy=10;Defence=50;MoveSpeed=1;AttackSpeed=1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>Attack=10;HP=100;Evasion=10;Accuracy=10;Defence=50;MoveSpeed=1;AttackSpeed=1</t>
   </si>
   <si>
-    <t>Attack=100;Hp=1000;Evasion=15;Accuracy=15;Defence=100;MoveSpeed=1;AttackSpeed=1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>Attack=100;HP=1000;Evasion=15;Accuracy=15;Defence=100;MoveSpeed=1;AttackSpeed=1</t>
   </si>
 </sst>
 </file>
